--- a/results/Int Task Remove ACC -0.3/Rando_1_permute.xlsx
+++ b/results/Int Task Remove ACC -0.3/Rando_1_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.699311242558242</v>
+        <v>0.7392966940408507</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7023463312850553</v>
+        <v>0.7392966940408507</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6847833993759451</v>
+        <v>0.7380204444954919</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6872076418001876</v>
+        <v>0.7389936637378204</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6915911483757347</v>
+        <v>0.7399412316468539</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6922228603150903</v>
+        <v>0.7389423610712302</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6928160952545034</v>
+        <v>0.7342045215260629</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6836867091636516</v>
+        <v>0.7345075518290932</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6813650720725895</v>
+        <v>0.7278152338291315</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6900038285572082</v>
+        <v>0.7279819674955492</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6931110855873963</v>
+        <v>0.7279819674955492</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6954759853749115</v>
+        <v>0.72620226267731</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6852707747085511</v>
+        <v>0.6943743180382473</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6849549187388733</v>
+        <v>0.6758990409464194</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6700614483431919</v>
+        <v>0.6662533739160397</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6659633607075174</v>
+        <v>0.6574831064913187</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6659377093742223</v>
+        <v>0.6536928348551848</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6558014127376098</v>
+        <v>0.6526602729761289</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6471241792530484</v>
+        <v>0.6148086678535194</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6404783782231667</v>
+        <v>0.6225976760657745</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6389375753747201</v>
+        <v>0.6235195926415131</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6281904324355367</v>
+        <v>0.6023202970960394</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6037636631635368</v>
+        <v>0.6101221309749421</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.604829916346025</v>
+        <v>0.6104251612779723</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6613826834357472</v>
+        <v>0.6078148509734107</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6569991768602002</v>
+        <v>0.6006142920040582</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.661767453435173</v>
+        <v>0.5864616474281666</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6441356074963149</v>
+        <v>0.5770420567009322</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5674268267003579</v>
+        <v>0.5781643982465208</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5674268267003579</v>
+        <v>0.578416125882961</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5636958977009514</v>
+        <v>0.5752367005493979</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5710679760332319</v>
+        <v>0.5711225329734489</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5710679760332319</v>
+        <v>0.5737215490342464</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5711192786998219</v>
+        <v>0.5685828595493788</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5714303489729895</v>
+        <v>0.576099274488409</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5711144930033117</v>
+        <v>0.576099274488409</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5701075824575509</v>
+        <v>0.5753312659124409</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5782974406095063</v>
+        <v>0.5699280231244855</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5612620838836885</v>
+        <v>0.5800771454277456</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5615907655200137</v>
+        <v>0.5800771454277456</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5635467753976914</v>
+        <v>0.578780030245602</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.559671509791535</v>
+        <v>0.5880200616397711</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5596634698213978</v>
+        <v>0.5853056145791459</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5571077164570531</v>
+        <v>0.6048599705201095</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5616483853059975</v>
+        <v>0.6023972510959245</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.561661210972645</v>
+        <v>0.6027387583988973</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5616740366392925</v>
+        <v>0.6045136775206263</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5634922184574743</v>
+        <v>0.6110905645207604</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5532693964279561</v>
+        <v>0.5958716667623806</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5548486762763453</v>
+        <v>0.6028285380654301</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5548486762763453</v>
+        <v>0.596793583338119</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5447717222764601</v>
+        <v>0.5966748980646643</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5251758264897873</v>
+        <v>0.6035724267309864</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.506134688642585</v>
+        <v>0.6009301479737361</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.509827140642049</v>
+        <v>0.5977313884262716</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5359549378816593</v>
+        <v>0.586342962154712</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5359549378816593</v>
+        <v>0.582228794578763</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5481883267290721</v>
+        <v>0.5819257642757327</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5445519630927085</v>
+        <v>0.5474363980933785</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.538650050728383</v>
+        <v>0.5483454890024694</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5341126361530657</v>
+        <v>0.5425879132448936</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5350473783954517</v>
+        <v>0.5575261777599112</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5428107352744118</v>
+        <v>0.5135498382434579</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5235241869101629</v>
+        <v>0.5162514596374357</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5050873868182776</v>
+        <v>0.5210614674859779</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5068799173031643</v>
+        <v>0.5165288386071709</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5021083864545646</v>
+        <v>0.51333180191045</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5002902046363827</v>
+        <v>0.5145952257891613</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4996841440303222</v>
+        <v>0.5176207431229541</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4996841440303222</v>
+        <v>0.5176207431229541</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4999871743333525</v>
+        <v>0.5179750760925745</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5011992955454737</v>
+        <v>0.5198830375772889</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.501502325848504</v>
+        <v>0.5040774134267502</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.500567583606118</v>
+        <v>0.4867566377610598</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5023472884243573</v>
+        <v>0.4726248588219529</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.502044258121327</v>
+        <v>0.4698192920997722</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.502044258121327</v>
+        <v>0.4647510480675358</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5017284021516492</v>
+        <v>0.4650540783705661</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5002260763031452</v>
+        <v>0.4598545148260877</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5041350332127338</v>
+        <v>0.4974880836156894</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.504954344455292</v>
+        <v>0.4935197840693735</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5012842895154961</v>
+        <v>0.4730674400352227</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5012842895154961</v>
+        <v>0.4866266582438408</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4990091693945137</v>
+        <v>0.4948950018185647</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4999823886368422</v>
+        <v>0.493277244970233</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4991839430310688</v>
+        <v>0.4945534945155918</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4999102203334673</v>
+        <v>0.4980407358486954</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4995045846972569</v>
+        <v>0.4980022588487529</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.498621145121461</v>
+        <v>0.4967644863033366</v>
       </c>
     </row>
   </sheetData>
